--- a/Unity/Assets/Config/Excel/Datas/StartConfig/Benchmark/StartProcessConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/StartConfig/Benchmark/StartProcessConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ETPlus\Unity\Assets\Config\Excel\Datas\StartConfig\Benchmark\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\EP-ET-Luban\Unity\Assets\Config\Excel\StartConfig\Benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C1FE27-6964-4741-85D3-F9F0F93B3075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46096EB1-FA45-45A7-BD1A-8FCA10D1122B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="2265" windowWidth="20775" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartProcessConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>内网端口</t>
   </si>
@@ -50,9 +50,6 @@
   <si>
     <t>所属机器</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
   </si>
   <si>
     <t>Port</t>
@@ -63,7 +60,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,28 +99,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -155,7 +134,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -163,13 +142,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -180,9 +152,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -191,14 +160,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="差 2" xfId="3" xr:uid="{B9E214A7-9577-4A27-A86F-BAA55A3CDA9C}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="5" xr:uid="{773B7DDD-ECAE-4C8D-9C1F-72F2AFB3A265}"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
-    <cellStyle name="好 2" xfId="4" xr:uid="{977EC2CB-5296-4484-9830-D5A6D69EDCE1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -500,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -509,480 +478,231 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" s="4" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A2" s="7" t="s">
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" s="4" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8">
         <v>20001</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+      <c r="B5" s="8">
         <v>2</v>
       </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
         <v>20002</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="4">
+      <c r="B6" s="8">
         <v>3</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8">
         <v>20003</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
         <v>20004</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>20005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="8">
+        <v>6</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>20006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="8">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>20007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="8">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4">
-        <v>20005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>20006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4">
-        <v>7</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>20007</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
         <v>20008</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4">
+      <c r="B12" s="8">
         <v>9</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
         <v>20009</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="B13" s="8">
         <v>10</v>
       </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
         <v>20010</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="B14" s="8">
         <v>11</v>
       </c>
-      <c r="C14" s="4">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8">
         <v>20011</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="B15" s="8">
         <v>12</v>
       </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C15" s="8">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8">
         <v>20012</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="4">
+      <c r="B16" s="8">
         <v>13</v>
       </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C16" s="8">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8">
         <v>20013</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="8">
         <v>14</v>
       </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="8">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8">
         <v>20014</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="8">
         <v>15</v>
       </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8">
         <v>20015</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="8">
         <v>16</v>
       </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="C19" s="8">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8">
         <v>20016</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="3">
-        <v>17</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4">
-        <v>20017</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="4">
-        <v>18</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4">
-        <v>20018</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="4">
-        <v>19</v>
-      </c>
-      <c r="C22" s="4">
-        <v>1</v>
-      </c>
-      <c r="D22" s="4">
-        <v>20019</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3">
-        <v>20</v>
-      </c>
-      <c r="C23" s="4">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4">
-        <v>20020</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="4">
-        <v>21</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4">
-        <v>20021</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="4">
-        <v>22</v>
-      </c>
-      <c r="C25" s="4">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4">
-        <v>20022</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="3">
-        <v>23</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4">
-        <v>20023</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="4">
-        <v>24</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4">
-        <v>20024</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="4">
-        <v>25</v>
-      </c>
-      <c r="C28" s="4">
-        <v>1</v>
-      </c>
-      <c r="D28" s="4">
-        <v>20025</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="3">
-        <v>26</v>
-      </c>
-      <c r="C29" s="4">
-        <v>1</v>
-      </c>
-      <c r="D29" s="4">
-        <v>20026</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="4">
-        <v>27</v>
-      </c>
-      <c r="C30" s="4">
-        <v>1</v>
-      </c>
-      <c r="D30" s="4">
-        <v>20027</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="4">
-        <v>28</v>
-      </c>
-      <c r="C31" s="4">
-        <v>1</v>
-      </c>
-      <c r="D31" s="4">
-        <v>20028</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="3">
-        <v>29</v>
-      </c>
-      <c r="C32" s="4">
-        <v>1</v>
-      </c>
-      <c r="D32" s="4">
-        <v>20029</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="4">
-        <v>30</v>
-      </c>
-      <c r="C33" s="4">
-        <v>1</v>
-      </c>
-      <c r="D33" s="4">
-        <v>20030</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="4">
-        <v>31</v>
-      </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-      <c r="D34" s="4">
-        <v>20031</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>